--- a/docs/downloads/09/t8_transition_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/09/t8_transition_alaotra_ambohidrony.xlsx
@@ -443,12 +443,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
